--- a/IDEA/benchmark/data/eval_data_11-17-25.xlsx
+++ b/IDEA/benchmark/data/eval_data_11-17-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,6 +456,11 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>google/gemini-3-pro-preview</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>openai/gpt-5</t>
         </is>
       </c>
@@ -468,32 +473,37 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>656/720 -&gt; 0.9111</t>
+          <t>656/720 -&gt; 91.11%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>682/720 -&gt; 0.9472</t>
+          <t>682/720 -&gt; 94.72%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>682/720 -&gt; 0.9472</t>
+          <t>682/720 -&gt; 94.72%</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>642/720 -&gt; 0.8917</t>
+          <t>642/720 -&gt; 89.17%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>663/720 -&gt; 0.9208</t>
+          <t>663/720 -&gt; 92.08%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>631/720 -&gt; 0.8764</t>
+          <t>675/720 -&gt; 93.75%</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>631/720 -&gt; 87.64%</t>
         </is>
       </c>
     </row>
@@ -505,32 +515,37 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>124/150 -&gt; 0.8267</t>
+          <t>124/150 -&gt; 82.67%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>129/150 -&gt; 0.8600</t>
+          <t>129/150 -&gt; 86.00%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>132/150 -&gt; 0.8800</t>
+          <t>132/150 -&gt; 88.00%</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>108/150 -&gt; 0.7200</t>
+          <t>108/150 -&gt; 72.00%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>120/150 -&gt; 0.8000</t>
+          <t>120/150 -&gt; 80.00%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>105/150 -&gt; 0.7000</t>
+          <t>130/150 -&gt; 86.67%</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>105/150 -&gt; 70.00%</t>
         </is>
       </c>
     </row>
@@ -542,32 +557,37 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>190/210 -&gt; 0.9048</t>
+          <t>190/210 -&gt; 90.48%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>192/210 -&gt; 0.9143</t>
+          <t>192/210 -&gt; 91.43%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>197/210 -&gt; 0.9381</t>
+          <t>197/210 -&gt; 93.81%</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>180/210 -&gt; 0.8571</t>
+          <t>180/210 -&gt; 85.71%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>195/210 -&gt; 0.9286</t>
+          <t>195/210 -&gt; 92.86%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>175/210 -&gt; 0.8333</t>
+          <t>201/210 -&gt; 95.71%</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>175/210 -&gt; 83.33%</t>
         </is>
       </c>
     </row>
@@ -579,32 +599,37 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24/30 -&gt; 0.8000</t>
+          <t>24/30 -&gt; 80.00%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>24/30 -&gt; 0.8000</t>
+          <t>24/30 -&gt; 80.00%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>21/30 -&gt; 0.7000</t>
+          <t>21/30 -&gt; 70.00%</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>21/30 -&gt; 0.7000</t>
+          <t>21/30 -&gt; 70.00%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>27/30 -&gt; 0.9000</t>
+          <t>27/30 -&gt; 90.00%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>23/30 -&gt; 0.7667</t>
+          <t>26/30 -&gt; 86.67%</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>23/30 -&gt; 76.67%</t>
         </is>
       </c>
     </row>
@@ -616,32 +641,37 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>30/30 -&gt; 1.0000</t>
+          <t>30/30 -&gt; 100.00%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>30/30 -&gt; 1.0000</t>
+          <t>30/30 -&gt; 100.00%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>30/30 -&gt; 1.0000</t>
+          <t>30/30 -&gt; 100.00%</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>30/30 -&gt; 1.0000</t>
+          <t>30/30 -&gt; 100.00%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>30/30 -&gt; 1.0000</t>
+          <t>30/30 -&gt; 100.00%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>30/30 -&gt; 1.0000</t>
+          <t>30/30 -&gt; 100.00%</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>30/30 -&gt; 100.00%</t>
         </is>
       </c>
     </row>
@@ -653,32 +683,37 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>30/30 -&gt; 1.0000</t>
+          <t>30/30 -&gt; 100.00%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>29/30 -&gt; 0.9667</t>
+          <t>29/30 -&gt; 96.67%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>29/30 -&gt; 0.9667</t>
+          <t>29/30 -&gt; 96.67%</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>27/30 -&gt; 0.9000</t>
+          <t>27/30 -&gt; 90.00%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>29/30 -&gt; 0.9667</t>
+          <t>29/30 -&gt; 96.67%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>29/30 -&gt; 0.9667</t>
+          <t>29/30 -&gt; 96.67%</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>29/30 -&gt; 96.67%</t>
         </is>
       </c>
     </row>
@@ -690,32 +725,37 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>30/30 -&gt; 1.0000</t>
+          <t>30/30 -&gt; 100.00%</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>30/30 -&gt; 1.0000</t>
+          <t>30/30 -&gt; 100.00%</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>30/30 -&gt; 1.0000</t>
+          <t>30/30 -&gt; 100.00%</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>29/30 -&gt; 0.9667</t>
+          <t>29/30 -&gt; 96.67%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>29/30 -&gt; 0.9667</t>
+          <t>29/30 -&gt; 96.67%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>29/30 -&gt; 0.9667</t>
+          <t>29/30 -&gt; 96.67%</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>29/30 -&gt; 96.67%</t>
         </is>
       </c>
     </row>
@@ -727,32 +767,37 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>21/30 -&gt; 0.7000</t>
+          <t>21/30 -&gt; 70.00%</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>23/30 -&gt; 0.7667</t>
+          <t>23/30 -&gt; 76.67%</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>30/30 -&gt; 1.0000</t>
+          <t>30/30 -&gt; 100.00%</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>29/30 -&gt; 0.9667</t>
+          <t>29/30 -&gt; 96.67%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>29/30 -&gt; 0.9667</t>
+          <t>29/30 -&gt; 96.67%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>28/30 -&gt; 0.9333</t>
+          <t>29/30 -&gt; 96.67%</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>28/30 -&gt; 93.33%</t>
         </is>
       </c>
     </row>
@@ -764,32 +809,37 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>29/30 -&gt; 0.9667</t>
+          <t>29/30 -&gt; 96.67%</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>30/30 -&gt; 1.0000</t>
+          <t>30/30 -&gt; 100.00%</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>28/30 -&gt; 0.9333</t>
+          <t>28/30 -&gt; 93.33%</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>30/30 -&gt; 1.0000</t>
+          <t>30/30 -&gt; 100.00%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>30/30 -&gt; 1.0000</t>
+          <t>30/30 -&gt; 100.00%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>30/30 -&gt; 1.0000</t>
+          <t>29/30 -&gt; 96.67%</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>30/30 -&gt; 100.00%</t>
         </is>
       </c>
     </row>
@@ -801,32 +851,37 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>26/30 -&gt; 0.8667</t>
+          <t>26/30 -&gt; 86.67%</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>26/30 -&gt; 0.8667</t>
+          <t>26/30 -&gt; 86.67%</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>29/30 -&gt; 0.9667</t>
+          <t>29/30 -&gt; 96.67%</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>14/30 -&gt; 0.4667</t>
+          <t>14/30 -&gt; 46.67%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>21/30 -&gt; 0.7000</t>
+          <t>21/30 -&gt; 70.00%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>6/30 -&gt; 0.2000</t>
+          <t>29/30 -&gt; 96.67%</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>6/30 -&gt; 20.00%</t>
         </is>
       </c>
     </row>
@@ -838,32 +893,37 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>21/30 -&gt; 0.7000</t>
+          <t>21/30 -&gt; 70.00%</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>23/30 -&gt; 0.7667</t>
+          <t>23/30 -&gt; 76.67%</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>20/30 -&gt; 0.6667</t>
+          <t>20/30 -&gt; 66.67%</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>13/30 -&gt; 0.4333</t>
+          <t>13/30 -&gt; 43.33%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>22/30 -&gt; 0.7333</t>
+          <t>22/30 -&gt; 73.33%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>11/30 -&gt; 0.3667</t>
+          <t>26/30 -&gt; 86.67%</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>11/30 -&gt; 36.67%</t>
         </is>
       </c>
     </row>
@@ -875,32 +935,37 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>172/180 -&gt; 0.9556</t>
+          <t>172/180 -&gt; 95.56%</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>177/180 -&gt; 0.9833</t>
+          <t>177/180 -&gt; 98.33%</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>178/180 -&gt; 0.9889</t>
+          <t>178/180 -&gt; 98.89%</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>159/180 -&gt; 0.8833</t>
+          <t>159/180 -&gt; 88.33%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>165/180 -&gt; 0.9167</t>
+          <t>165/180 -&gt; 91.67%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>155/180 -&gt; 0.8611</t>
+          <t>170/180 -&gt; 94.44%</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>155/180 -&gt; 86.11%</t>
         </is>
       </c>
     </row>
@@ -912,32 +977,37 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>30/30 -&gt; 1.0000</t>
+          <t>30/30 -&gt; 100.00%</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>29/30 -&gt; 0.9667</t>
+          <t>29/30 -&gt; 96.67%</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>30/30 -&gt; 1.0000</t>
+          <t>30/30 -&gt; 100.00%</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>30/30 -&gt; 1.0000</t>
+          <t>30/30 -&gt; 100.00%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>30/30 -&gt; 1.0000</t>
+          <t>30/30 -&gt; 100.00%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>30/30 -&gt; 1.0000</t>
+          <t>30/30 -&gt; 100.00%</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>30/30 -&gt; 100.00%</t>
         </is>
       </c>
     </row>
@@ -949,32 +1019,37 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>29/30 -&gt; 0.9667</t>
+          <t>29/30 -&gt; 96.67%</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>30/30 -&gt; 1.0000</t>
+          <t>30/30 -&gt; 100.00%</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>30/30 -&gt; 1.0000</t>
+          <t>30/30 -&gt; 100.00%</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>30/30 -&gt; 1.0000</t>
+          <t>30/30 -&gt; 100.00%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>30/30 -&gt; 1.0000</t>
+          <t>30/30 -&gt; 100.00%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>30/30 -&gt; 1.0000</t>
+          <t>30/30 -&gt; 100.00%</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>30/30 -&gt; 100.00%</t>
         </is>
       </c>
     </row>
@@ -986,32 +1061,37 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>30/30 -&gt; 1.0000</t>
+          <t>30/30 -&gt; 100.00%</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>30/30 -&gt; 1.0000</t>
+          <t>30/30 -&gt; 100.00%</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>30/30 -&gt; 1.0000</t>
+          <t>30/30 -&gt; 100.00%</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>30/30 -&gt; 1.0000</t>
+          <t>30/30 -&gt; 100.00%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>30/30 -&gt; 1.0000</t>
+          <t>30/30 -&gt; 100.00%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>30/30 -&gt; 1.0000</t>
+          <t>30/30 -&gt; 100.00%</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>30/30 -&gt; 100.00%</t>
         </is>
       </c>
     </row>
@@ -1023,32 +1103,37 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>28/30 -&gt; 0.9333</t>
+          <t>28/30 -&gt; 93.33%</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>29/30 -&gt; 0.9667</t>
+          <t>29/30 -&gt; 96.67%</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>29/30 -&gt; 0.9667</t>
+          <t>29/30 -&gt; 96.67%</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>24/30 -&gt; 0.8000</t>
+          <t>24/30 -&gt; 80.00%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>25/30 -&gt; 0.8333</t>
+          <t>25/30 -&gt; 83.33%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>23/30 -&gt; 0.7667</t>
+          <t>27/30 -&gt; 90.00%</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>23/30 -&gt; 76.67%</t>
         </is>
       </c>
     </row>
@@ -1060,32 +1145,37 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>28/30 -&gt; 0.9333</t>
+          <t>28/30 -&gt; 93.33%</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>30/30 -&gt; 1.0000</t>
+          <t>30/30 -&gt; 100.00%</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>30/30 -&gt; 1.0000</t>
+          <t>30/30 -&gt; 100.00%</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>27/30 -&gt; 0.9000</t>
+          <t>27/30 -&gt; 90.00%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>30/30 -&gt; 1.0000</t>
+          <t>30/30 -&gt; 100.00%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>28/30 -&gt; 0.9333</t>
+          <t>29/30 -&gt; 96.67%</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>28/30 -&gt; 93.33%</t>
         </is>
       </c>
     </row>
@@ -1097,32 +1187,37 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>27/30 -&gt; 0.9000</t>
+          <t>27/30 -&gt; 90.00%</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>29/30 -&gt; 0.9667</t>
+          <t>29/30 -&gt; 96.67%</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>29/30 -&gt; 0.9667</t>
+          <t>29/30 -&gt; 96.67%</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>18/30 -&gt; 0.6000</t>
+          <t>18/30 -&gt; 60.00%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>20/30 -&gt; 0.6667</t>
+          <t>20/30 -&gt; 66.67%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>14/30 -&gt; 0.4667</t>
+          <t>24/30 -&gt; 80.00%</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>14/30 -&gt; 46.67%</t>
         </is>
       </c>
     </row>
@@ -1134,32 +1229,37 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>28/30 -&gt; 0.9333</t>
+          <t>28/30 -&gt; 93.33%</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>28/30 -&gt; 0.9333</t>
+          <t>28/30 -&gt; 93.33%</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>29/30 -&gt; 0.9667</t>
+          <t>29/30 -&gt; 96.67%</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>24/30 -&gt; 0.8000</t>
+          <t>24/30 -&gt; 80.00%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>25/30 -&gt; 0.8333</t>
+          <t>25/30 -&gt; 83.33%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>23/30 -&gt; 0.7667</t>
+          <t>27/30 -&gt; 90.00%</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>23/30 -&gt; 76.67%</t>
         </is>
       </c>
     </row>
@@ -1171,32 +1271,37 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>82/90 -&gt; 0.9111</t>
+          <t>82/90 -&gt; 91.11%</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>86/90 -&gt; 0.9556</t>
+          <t>86/90 -&gt; 95.56%</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>86/90 -&gt; 0.9556</t>
+          <t>86/90 -&gt; 95.56%</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>79/90 -&gt; 0.8778</t>
+          <t>79/90 -&gt; 87.78%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>80/90 -&gt; 0.8889</t>
+          <t>80/90 -&gt; 88.89%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>77/90 -&gt; 0.8556</t>
+          <t>81/90 -&gt; 90.00%</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>77/90 -&gt; 85.56%</t>
         </is>
       </c>
     </row>
@@ -1208,32 +1313,37 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>25/30 -&gt; 0.8333</t>
+          <t>25/30 -&gt; 83.33%</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>30/30 -&gt; 1.0000</t>
+          <t>30/30 -&gt; 100.00%</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>29/30 -&gt; 0.9667</t>
+          <t>29/30 -&gt; 96.67%</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>27/30 -&gt; 0.9000</t>
+          <t>27/30 -&gt; 90.00%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>28/30 -&gt; 0.9333</t>
+          <t>28/30 -&gt; 93.33%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>28/30 -&gt; 0.9333</t>
+          <t>28/30 -&gt; 93.33%</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>28/30 -&gt; 93.33%</t>
         </is>
       </c>
     </row>
@@ -1245,32 +1355,37 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>29/30 -&gt; 0.9667</t>
+          <t>29/30 -&gt; 96.67%</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>29/30 -&gt; 0.9667</t>
+          <t>29/30 -&gt; 96.67%</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>29/30 -&gt; 0.9667</t>
+          <t>29/30 -&gt; 96.67%</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>24/30 -&gt; 0.8000</t>
+          <t>24/30 -&gt; 80.00%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>23/30 -&gt; 0.7667</t>
+          <t>23/30 -&gt; 76.67%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>21/30 -&gt; 0.7000</t>
+          <t>25/30 -&gt; 83.33%</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>21/30 -&gt; 70.00%</t>
         </is>
       </c>
     </row>
@@ -1282,32 +1397,37 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>28/30 -&gt; 0.9333</t>
+          <t>28/30 -&gt; 93.33%</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>27/30 -&gt; 0.9000</t>
+          <t>27/30 -&gt; 90.00%</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>28/30 -&gt; 0.9333</t>
+          <t>28/30 -&gt; 93.33%</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>28/30 -&gt; 0.9333</t>
+          <t>28/30 -&gt; 93.33%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>29/30 -&gt; 0.9667</t>
+          <t>29/30 -&gt; 96.67%</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>28/30 -&gt; 0.9333</t>
+          <t>28/30 -&gt; 93.33%</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>28/30 -&gt; 93.33%</t>
         </is>
       </c>
     </row>
@@ -1319,32 +1439,37 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>27/30 -&gt; 0.9000</t>
+          <t>27/30 -&gt; 90.00%</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>26/30 -&gt; 0.8667</t>
+          <t>26/30 -&gt; 86.67%</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>29/30 -&gt; 0.9667</t>
+          <t>29/30 -&gt; 96.67%</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>23/30 -&gt; 0.7667</t>
+          <t>23/30 -&gt; 76.67%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>24/30 -&gt; 0.8000</t>
+          <t>24/30 -&gt; 80.00%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>21/30 -&gt; 0.7000</t>
+          <t>25/30 -&gt; 83.33%</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>21/30 -&gt; 70.00%</t>
         </is>
       </c>
     </row>
@@ -1356,32 +1481,37 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>81/90 -&gt; 0.9000</t>
+          <t>81/90 -&gt; 90.00%</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>83/90 -&gt; 0.9222</t>
+          <t>83/90 -&gt; 92.22%</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>87/90 -&gt; 0.9667</t>
+          <t>87/90 -&gt; 96.67%</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>83/90 -&gt; 0.9222</t>
+          <t>83/90 -&gt; 92.22%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>80/90 -&gt; 0.8889</t>
+          <t>80/90 -&gt; 88.89%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>82/90 -&gt; 0.9111</t>
+          <t>81/90 -&gt; 90.00%</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>82/90 -&gt; 91.11%</t>
         </is>
       </c>
     </row>
@@ -1393,32 +1523,37 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>25/30 -&gt; 0.8333</t>
+          <t>25/30 -&gt; 83.33%</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>30/30 -&gt; 1.0000</t>
+          <t>30/30 -&gt; 100.00%</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>29/30 -&gt; 0.9667</t>
+          <t>29/30 -&gt; 96.67%</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>29/30 -&gt; 0.9667</t>
+          <t>29/30 -&gt; 96.67%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>26/30 -&gt; 0.8667</t>
+          <t>26/30 -&gt; 86.67%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>29/30 -&gt; 0.9667</t>
+          <t>27/30 -&gt; 90.00%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>29/30 -&gt; 96.67%</t>
         </is>
       </c>
     </row>
@@ -1430,32 +1565,37 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>29/30 -&gt; 0.9667</t>
+          <t>29/30 -&gt; 96.67%</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>27/30 -&gt; 0.9000</t>
+          <t>27/30 -&gt; 90.00%</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>30/30 -&gt; 1.0000</t>
+          <t>30/30 -&gt; 100.00%</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>28/30 -&gt; 0.9333</t>
+          <t>28/30 -&gt; 93.33%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>29/30 -&gt; 0.9667</t>
+          <t>29/30 -&gt; 96.67%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>28/30 -&gt; 0.9333</t>
+          <t>28/30 -&gt; 93.33%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>28/30 -&gt; 93.33%</t>
         </is>
       </c>
     </row>
@@ -1467,32 +1607,37 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>27/30 -&gt; 0.9000</t>
+          <t>27/30 -&gt; 90.00%</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>26/30 -&gt; 0.8667</t>
+          <t>26/30 -&gt; 86.67%</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>28/30 -&gt; 0.9333</t>
+          <t>28/30 -&gt; 93.33%</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>26/30 -&gt; 0.8667</t>
+          <t>26/30 -&gt; 86.67%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>25/30 -&gt; 0.8333</t>
+          <t>25/30 -&gt; 83.33%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>25/30 -&gt; 0.8333</t>
+          <t>26/30 -&gt; 86.67%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>25/30 -&gt; 83.33%</t>
         </is>
       </c>
     </row>
@@ -1504,32 +1649,37 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>25/30 -&gt; 0.8333</t>
+          <t>25/30 -&gt; 83.33%</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>25/30 -&gt; 0.8333</t>
+          <t>25/30 -&gt; 83.33%</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>28/30 -&gt; 0.9333</t>
+          <t>28/30 -&gt; 93.33%</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>24/30 -&gt; 0.8000</t>
+          <t>24/30 -&gt; 80.00%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>23/30 -&gt; 0.7667</t>
+          <t>23/30 -&gt; 76.67%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>25/30 -&gt; 0.8333</t>
+          <t>27/30 -&gt; 90.00%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>25/30 -&gt; 83.33%</t>
         </is>
       </c>
     </row>
@@ -1541,32 +1691,37 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>131/150 -&gt; 0.8733</t>
+          <t>131/150 -&gt; 87.33%</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>144/150 -&gt; 0.9600</t>
+          <t>144/150 -&gt; 96.00%</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>134/150 -&gt; 0.8933</t>
+          <t>134/150 -&gt; 89.33%</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>141/150 -&gt; 0.9400</t>
+          <t>141/150 -&gt; 94.00%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>143/150 -&gt; 0.9533</t>
+          <t>143/150 -&gt; 95.33%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>142/150 -&gt; 0.9467</t>
+          <t>142/150 -&gt; 94.67%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>142/150 -&gt; 94.67%</t>
         </is>
       </c>
     </row>
@@ -1578,32 +1733,37 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>27/30 -&gt; 0.9000</t>
+          <t>27/30 -&gt; 90.00%</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>27/30 -&gt; 0.9000</t>
+          <t>27/30 -&gt; 90.00%</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>27/30 -&gt; 0.9000</t>
+          <t>27/30 -&gt; 90.00%</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>26/30 -&gt; 0.8667</t>
+          <t>26/30 -&gt; 86.67%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>27/30 -&gt; 0.9000</t>
+          <t>27/30 -&gt; 90.00%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>27/30 -&gt; 0.9000</t>
+          <t>28/30 -&gt; 93.33%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>27/30 -&gt; 90.00%</t>
         </is>
       </c>
     </row>
@@ -1615,32 +1775,37 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>22/30 -&gt; 0.7333</t>
+          <t>22/30 -&gt; 73.33%</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>30/30 -&gt; 1.0000</t>
+          <t>30/30 -&gt; 100.00%</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>24/30 -&gt; 0.8000</t>
+          <t>24/30 -&gt; 80.00%</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>29/30 -&gt; 0.9667</t>
+          <t>29/30 -&gt; 96.67%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>29/30 -&gt; 0.9667</t>
+          <t>29/30 -&gt; 96.67%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>29/30 -&gt; 0.9667</t>
+          <t>29/30 -&gt; 96.67%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>29/30 -&gt; 96.67%</t>
         </is>
       </c>
     </row>
@@ -1652,32 +1817,37 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>25/30 -&gt; 0.8333</t>
+          <t>25/30 -&gt; 83.33%</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>29/30 -&gt; 0.9667</t>
+          <t>29/30 -&gt; 96.67%</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>26/30 -&gt; 0.8667</t>
+          <t>26/30 -&gt; 86.67%</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>28/30 -&gt; 0.9333</t>
+          <t>28/30 -&gt; 93.33%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>28/30 -&gt; 0.9333</t>
+          <t>28/30 -&gt; 93.33%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>28/30 -&gt; 0.9333</t>
+          <t>28/30 -&gt; 93.33%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>28/30 -&gt; 93.33%</t>
         </is>
       </c>
     </row>
@@ -1689,32 +1859,37 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>28/30 -&gt; 0.9333</t>
+          <t>28/30 -&gt; 93.33%</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>29/30 -&gt; 0.9667</t>
+          <t>29/30 -&gt; 96.67%</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>28/30 -&gt; 0.9333</t>
+          <t>28/30 -&gt; 93.33%</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>28/30 -&gt; 0.9333</t>
+          <t>28/30 -&gt; 93.33%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>29/30 -&gt; 0.9667</t>
+          <t>29/30 -&gt; 96.67%</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>29/30 -&gt; 0.9667</t>
+          <t>28/30 -&gt; 93.33%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>29/30 -&gt; 96.67%</t>
         </is>
       </c>
     </row>
@@ -1726,32 +1901,37 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>29/30 -&gt; 0.9667</t>
+          <t>29/30 -&gt; 96.67%</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>29/30 -&gt; 0.9667</t>
+          <t>29/30 -&gt; 96.67%</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>29/30 -&gt; 0.9667</t>
+          <t>29/30 -&gt; 96.67%</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>30/30 -&gt; 1.0000</t>
+          <t>30/30 -&gt; 100.00%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>30/30 -&gt; 1.0000</t>
+          <t>30/30 -&gt; 100.00%</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>29/30 -&gt; 0.9667</t>
+          <t>29/30 -&gt; 96.67%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>29/30 -&gt; 96.67%</t>
         </is>
       </c>
     </row>
@@ -1763,32 +1943,37 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>23/30 -&gt; 0.7667</t>
+          <t>23/30 -&gt; 76.67%</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>27/30 -&gt; 0.9000</t>
+          <t>27/30 -&gt; 90.00%</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>26/30 -&gt; 0.8667</t>
+          <t>26/30 -&gt; 86.67%</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>24/30 -&gt; 0.8000</t>
+          <t>24/30 -&gt; 80.00%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>26/30 -&gt; 0.8667</t>
+          <t>26/30 -&gt; 86.67%</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>25/30 -&gt; 0.8333</t>
+          <t>25/30 -&gt; 83.33%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>25/30 -&gt; 83.33%</t>
         </is>
       </c>
     </row>
@@ -1800,32 +1985,37 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0/0 -&gt; 0.0000</t>
+          <t>0/0 -&gt; 0.00%</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>0/0 -&gt; 0.0000</t>
+          <t>0/0 -&gt; 0.00%</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0/0 -&gt; 0.0000</t>
+          <t>0/0 -&gt; 0.00%</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>29/55 -&gt; 0.5273</t>
+          <t>29/55 -&gt; 52.73%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>51/73 -&gt; 0.6986</t>
+          <t>51/73 -&gt; 69.86%</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>41/83 -&gt; 0.4940</t>
+          <t>9/13 -&gt; 69.23%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>41/83 -&gt; 49.40%</t>
         </is>
       </c>
     </row>
@@ -1837,32 +2027,37 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0/0 -&gt; 0.0000</t>
+          <t>0/0 -&gt; 0.00%</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>0/0 -&gt; 0.0000</t>
+          <t>0/0 -&gt; 0.00%</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>0/0 -&gt; 0.0000</t>
+          <t>0/0 -&gt; 0.00%</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>613/665 -&gt; 0.9218</t>
+          <t>613/665 -&gt; 92.18%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>612/647 -&gt; 0.9459</t>
+          <t>612/647 -&gt; 94.59%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>590/637 -&gt; 0.9262</t>
+          <t>666/707 -&gt; 94.20%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>590/637 -&gt; 92.62%</t>
         </is>
       </c>
     </row>
